--- a/Course_Request_Report_2026_27.xlsx
+++ b/Course_Request_Report_2026_27.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,25 +132,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1351,13 +1348,13 @@
         <v>26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="29">
@@ -1438,13 +1435,13 @@
         <v>5</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="11" t="n">
-        <v>0</v>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2656,13 +2653,13 @@
         <v>24</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>0.7083333333333335</v>
+        <v>0.7916666666666665</v>
       </c>
     </row>
     <row r="74">
@@ -2946,13 +2943,13 @@
         <v>99</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.9898989898989899</v>
+        <v>0.9797979797979798</v>
       </c>
     </row>
     <row r="84">
@@ -3033,13 +3030,13 @@
         <v>36</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.9166666666666665</v>
+        <v>0.8611111111111112</v>
       </c>
     </row>
     <row r="87">
@@ -3091,13 +3088,13 @@
         <v>39</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.9487179487179486</v>
+        <v>0.7948717948717949</v>
       </c>
     </row>
     <row r="89">
@@ -3178,13 +3175,13 @@
         <v>31</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="G91" s="11" t="n">
-        <v>0</v>
+      <c r="F91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3468,13 +3465,13 @@
         <v>59</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G101" s="14" t="n">
-        <v>0.864406779661017</v>
+        <v>13</v>
+      </c>
+      <c r="G101" s="11" t="n">
+        <v>0.7796610169491526</v>
       </c>
     </row>
     <row r="102">
@@ -3497,13 +3494,13 @@
         <v>63</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" s="13" t="n">
-        <v>0.9523809523809522</v>
+        <v>5</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>0.9206349206349206</v>
       </c>
     </row>
     <row r="103">
@@ -3729,13 +3726,13 @@
         <v>8</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G110" s="15" t="n">
-        <v>0</v>
+      <c r="F110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3787,13 +3784,13 @@
         <v>61</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F112" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G112" s="13" t="n">
-        <v>0.9180327868852458</v>
+        <v>6</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>0.901639344262295</v>
       </c>
     </row>
     <row r="113">
@@ -3903,13 +3900,13 @@
         <v>75</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G116" s="13" t="n">
-        <v>0.92</v>
+        <v>4</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>0.9466666666666668</v>
       </c>
     </row>
     <row r="117">
@@ -4222,13 +4219,13 @@
         <v>58</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F127" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G127" s="12" t="n">
-        <v>0.9310344827586207</v>
+        <v>6</v>
+      </c>
+      <c r="G127" s="11" t="n">
+        <v>0.896551724137931</v>
       </c>
     </row>
     <row r="128">
@@ -4512,13 +4509,13 @@
         <v>165</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" s="10" t="n">
         <v>165</v>
       </c>
-      <c r="G137" s="11" t="n">
-        <v>0</v>
+      <c r="F137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -4662,7 +4659,7 @@
       <c r="F142" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G142" s="15" t="n">
+      <c r="G142" s="9" t="n">
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -4686,13 +4683,13 @@
         <v>13</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F143" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G143" s="14" t="n">
-        <v>0.7692307692307694</v>
+        <v>1</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="144">
@@ -4715,34 +4712,34 @@
         <v>33</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G144" s="9" t="n">
-        <v>0.8787878787878788</v>
+        <v>7</v>
+      </c>
+      <c r="G144" s="13" t="n">
+        <v>0.7878787878787878</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="16" t="inlineStr"/>
-      <c r="B145" s="17" t="inlineStr">
+      <c r="A145" s="15" t="inlineStr"/>
+      <c r="B145" s="16" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C145" s="16" t="inlineStr"/>
-      <c r="D145" s="18" t="n">
+      <c r="C145" s="15" t="inlineStr"/>
+      <c r="D145" s="17" t="n">
         <v>6538</v>
       </c>
-      <c r="E145" s="18" t="n">
-        <v>6274</v>
-      </c>
-      <c r="F145" s="18" t="n">
-        <v>264</v>
-      </c>
-      <c r="G145" s="19" t="n">
-        <v>0.9596206791067605</v>
+      <c r="E145" s="17" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F145" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="G145" s="18" t="n">
+        <v>0.9886815539920465</v>
       </c>
     </row>
   </sheetData>

--- a/Course_Request_Report_2026_27.xlsx
+++ b/Course_Request_Report_2026_27.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,28 +126,31 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,13 +626,13 @@
         <v>64</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.984375</v>
       </c>
     </row>
     <row r="4">
@@ -686,7 +689,7 @@
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -710,13 +713,13 @@
         <v>56</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -744,7 +747,7 @@
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -802,7 +805,7 @@
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -826,13 +829,13 @@
         <v>65</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>0.9538461538461539</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +863,7 @@
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -918,7 +921,7 @@
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -942,13 +945,13 @@
         <v>68</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.8970588235294117</v>
       </c>
     </row>
     <row r="15">
@@ -971,13 +974,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="16">
@@ -1000,13 +1003,13 @@
         <v>47</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
+        <v>46</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>0.9787234042553191</v>
       </c>
     </row>
     <row r="17">
@@ -1034,7 +1037,7 @@
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1087,13 +1090,13 @@
         <v>43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0.9534883720930233</v>
       </c>
     </row>
     <row r="20">
@@ -1116,13 +1119,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -1145,13 +1148,13 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
@@ -1174,13 +1177,13 @@
         <v>23</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="23">
@@ -1203,13 +1206,13 @@
         <v>4</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="24">
@@ -1232,13 +1235,13 @@
         <v>6</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -1261,13 +1264,13 @@
         <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="26">
@@ -1319,13 +1322,13 @@
         <v>2</v>
       </c>
       <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="G27" s="13" t="n">
         <v>0</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1348,13 +1351,13 @@
         <v>26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>0.6923076923076923</v>
+        <v>12</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0.4615384615384615</v>
       </c>
     </row>
     <row r="29">
@@ -1377,13 +1380,13 @@
         <v>15</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.4666666666666666</v>
       </c>
     </row>
     <row r="30">
@@ -1406,13 +1409,13 @@
         <v>5</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -1435,13 +1438,13 @@
         <v>5</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
@@ -1464,13 +1467,13 @@
         <v>4</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="33">
@@ -1493,13 +1496,13 @@
         <v>2</v>
       </c>
       <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="G33" s="13" t="n">
         <v>0</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1522,13 +1525,13 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1551,13 +1554,13 @@
         <v>2</v>
       </c>
       <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="G35" s="13" t="n">
         <v>0</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1580,13 +1583,13 @@
         <v>121</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>113</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>0.9338842975206612</v>
       </c>
     </row>
     <row r="37">
@@ -1609,13 +1612,13 @@
         <v>24</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>0.9166666666666665</v>
       </c>
     </row>
     <row r="38">
@@ -1638,13 +1641,13 @@
         <v>40</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>0.725</v>
       </c>
     </row>
     <row r="39">
@@ -1667,13 +1670,13 @@
         <v>23</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="40">
@@ -1696,13 +1699,13 @@
         <v>83</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>0.9156626506024097</v>
       </c>
     </row>
     <row r="41">
@@ -1725,13 +1728,13 @@
         <v>49</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>0.7959183673469387</v>
       </c>
     </row>
     <row r="42">
@@ -1754,13 +1757,13 @@
         <v>37</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>0.9459459459459459</v>
       </c>
     </row>
     <row r="43">
@@ -1783,13 +1786,13 @@
         <v>17</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="44">
@@ -1812,13 +1815,13 @@
         <v>25</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="45">
@@ -1841,13 +1844,13 @@
         <v>48</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>0.8958333333333335</v>
       </c>
     </row>
     <row r="46">
@@ -1870,13 +1873,13 @@
         <v>75</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>1</v>
+        <v>69</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="47">
@@ -1899,13 +1902,13 @@
         <v>21</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="48">
@@ -1928,13 +1931,13 @@
         <v>12</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -1957,13 +1960,13 @@
         <v>31</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.6774193548387096</v>
       </c>
     </row>
     <row r="50">
@@ -1986,13 +1989,13 @@
         <v>32</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>0.53125</v>
       </c>
     </row>
     <row r="51">
@@ -2015,13 +2018,13 @@
         <v>6</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.1666666666666666</v>
       </c>
     </row>
     <row r="52">
@@ -2044,13 +2047,13 @@
         <v>23</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="53">
@@ -2078,7 +2081,7 @@
       <c r="F53" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2102,13 +2105,13 @@
         <v>15</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="55">
@@ -2131,13 +2134,13 @@
         <v>31</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>0.8709677419354839</v>
       </c>
     </row>
     <row r="56">
@@ -2189,13 +2192,13 @@
         <v>67</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>0.9402985074626866</v>
       </c>
     </row>
     <row r="58">
@@ -2247,13 +2250,13 @@
         <v>25</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="60">
@@ -2276,13 +2279,13 @@
         <v>86</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>0.9767441860465115</v>
       </c>
     </row>
     <row r="61">
@@ -2305,13 +2308,13 @@
         <v>62</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>0.9354838709677419</v>
       </c>
     </row>
     <row r="62">
@@ -2334,13 +2337,13 @@
         <v>23</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>0.9130434782608695</v>
       </c>
     </row>
     <row r="63">
@@ -2363,13 +2366,13 @@
         <v>18</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>0.8333333333333335</v>
       </c>
     </row>
     <row r="64">
@@ -2392,13 +2395,13 @@
         <v>101</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="11" t="n">
+        <v>0.9801980198019803</v>
       </c>
     </row>
     <row r="65">
@@ -2426,7 +2429,7 @@
       <c r="F65" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2450,13 +2453,13 @@
         <v>19</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="67">
@@ -2479,13 +2482,13 @@
         <v>20</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="68">
@@ -2508,13 +2511,13 @@
         <v>25</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="69">
@@ -2537,13 +2540,13 @@
         <v>21</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="70">
@@ -2566,13 +2569,13 @@
         <v>16</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="11" t="n">
+        <v>0.9375</v>
       </c>
     </row>
     <row r="71">
@@ -2600,7 +2603,7 @@
       <c r="F71" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2624,13 +2627,13 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" s="14" t="n">
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="73">
@@ -2653,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F73" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" s="11" t="n">
-        <v>0.7916666666666665</v>
+        <v>9</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="74">
@@ -2682,13 +2685,13 @@
         <v>6</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" s="14" t="n">
+        <v>0.1666666666666666</v>
       </c>
     </row>
     <row r="75">
@@ -2711,13 +2714,13 @@
         <v>8</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="76">
@@ -2740,13 +2743,13 @@
         <v>5</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" s="14" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="77">
@@ -2769,13 +2772,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="78">
@@ -2798,13 +2801,13 @@
         <v>31</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G78" s="14" t="n">
+        <v>0.6129032258064516</v>
       </c>
     </row>
     <row r="79">
@@ -2827,13 +2830,13 @@
         <v>121</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>0.859504132231405</v>
       </c>
     </row>
     <row r="80">
@@ -2856,13 +2859,13 @@
         <v>93</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>1</v>
+        <v>88</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="11" t="n">
+        <v>0.946236559139785</v>
       </c>
     </row>
     <row r="81">
@@ -2885,13 +2888,13 @@
         <v>94</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="7" t="n">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>0.8617021276595744</v>
       </c>
     </row>
     <row r="82">
@@ -2914,13 +2917,13 @@
         <v>91</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v>1</v>
+        <v>89</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="11" t="n">
+        <v>0.978021978021978</v>
       </c>
     </row>
     <row r="83">
@@ -2943,13 +2946,13 @@
         <v>99</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="F83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>0.9797979797979798</v>
+        <v>93</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>0.9393939393939393</v>
       </c>
     </row>
     <row r="84">
@@ -2972,13 +2975,13 @@
         <v>67</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.835820895522388</v>
       </c>
     </row>
     <row r="85">
@@ -3001,13 +3004,13 @@
         <v>15</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="86">
@@ -3030,13 +3033,13 @@
         <v>36</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" s="13" t="n">
-        <v>0.8611111111111112</v>
+        <v>21</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G86" s="14" t="n">
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="87">
@@ -3059,13 +3062,13 @@
         <v>24</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="88">
@@ -3088,13 +3091,13 @@
         <v>39</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F88" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G88" s="13" t="n">
-        <v>0.7948717948717949</v>
+        <v>23</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G88" s="14" t="n">
+        <v>0.5897435897435898</v>
       </c>
     </row>
     <row r="89">
@@ -3117,13 +3120,13 @@
         <v>13</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="8" t="n">
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="90">
@@ -3146,13 +3149,13 @@
         <v>20</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="11" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="91">
@@ -3175,13 +3178,13 @@
         <v>31</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>0.7096774193548387</v>
       </c>
     </row>
     <row r="92">
@@ -3204,13 +3207,13 @@
         <v>20</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="93">
@@ -3233,13 +3236,13 @@
         <v>17</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F93" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>0.9411764705882352</v>
+        <v>5</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="94">
@@ -3262,13 +3265,13 @@
         <v>44</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="4" t="n">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="95">
@@ -3291,13 +3294,13 @@
         <v>17</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G95" s="13" t="n">
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="96">
@@ -3320,13 +3323,13 @@
         <v>20</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="97">
@@ -3349,13 +3352,13 @@
         <v>3</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="13" t="n">
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="98">
@@ -3378,13 +3381,13 @@
         <v>13</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="99">
@@ -3412,7 +3415,7 @@
       <c r="F99" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="7" t="n">
+      <c r="G99" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3465,13 +3468,13 @@
         <v>59</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="F101" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="G101" s="11" t="n">
-        <v>0.7796610169491526</v>
+        <v>45</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G101" s="15" t="n">
+        <v>0.7627118644067796</v>
       </c>
     </row>
     <row r="102">
@@ -3494,13 +3497,13 @@
         <v>63</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="F102" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G102" s="14" t="n">
-        <v>0.9206349206349206</v>
+        <v>52</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.8253968253968254</v>
       </c>
     </row>
     <row r="103">
@@ -3523,13 +3526,13 @@
         <v>132</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="7" t="n">
-        <v>1</v>
+        <v>88</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="G103" s="13" t="n">
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="104">
@@ -3552,13 +3555,13 @@
         <v>152</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v>1</v>
+        <v>149</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" s="11" t="n">
+        <v>0.9802631578947368</v>
       </c>
     </row>
     <row r="105">
@@ -3581,13 +3584,13 @@
         <v>38</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="n">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>0.7631578947368421</v>
       </c>
     </row>
     <row r="106">
@@ -3639,13 +3642,13 @@
         <v>128</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="7" t="n">
-        <v>1</v>
+        <v>126</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="8" t="n">
+        <v>0.984375</v>
       </c>
     </row>
     <row r="108">
@@ -3668,13 +3671,13 @@
         <v>62</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="4" t="n">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="11" t="n">
+        <v>0.9838709677419355</v>
       </c>
     </row>
     <row r="109">
@@ -3697,13 +3700,13 @@
         <v>29</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="8" t="n">
+        <v>0.9655172413793103</v>
       </c>
     </row>
     <row r="110">
@@ -3726,13 +3729,13 @@
         <v>8</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="111">
@@ -3755,13 +3758,13 @@
         <v>62</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="n">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="G111" s="13" t="n">
+        <v>0.4032258064516129</v>
       </c>
     </row>
     <row r="112">
@@ -3784,13 +3787,13 @@
         <v>61</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="F112" s="8" t="n">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>34</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>0.901639344262295</v>
+        <v>0.4426229508196721</v>
       </c>
     </row>
     <row r="113">
@@ -3813,13 +3816,13 @@
         <v>43</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="n">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G113" s="13" t="n">
+        <v>0.6511627906976745</v>
       </c>
     </row>
     <row r="114">
@@ -3842,13 +3845,13 @@
         <v>82</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="4" t="n">
-        <v>1</v>
+        <v>67</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.8170731707317073</v>
       </c>
     </row>
     <row r="115">
@@ -3871,13 +3874,13 @@
         <v>56</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="7" t="n">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G115" s="13" t="n">
+        <v>0.7321428571428571</v>
       </c>
     </row>
     <row r="116">
@@ -3900,13 +3903,13 @@
         <v>75</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="F116" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G116" s="14" t="n">
-        <v>0.9466666666666668</v>
+        <v>57</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="117">
@@ -3934,7 +3937,7 @@
       <c r="F117" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="7" t="n">
+      <c r="G117" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3958,13 +3961,13 @@
         <v>40</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="119">
@@ -3987,13 +3990,13 @@
         <v>59</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="7" t="n">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>0.8983050847457628</v>
       </c>
     </row>
     <row r="120">
@@ -4016,13 +4019,13 @@
         <v>29</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>0.6551724137931035</v>
       </c>
     </row>
     <row r="121">
@@ -4050,7 +4053,7 @@
       <c r="F121" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G121" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4074,13 +4077,13 @@
         <v>33</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" s="4" t="n">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G122" s="14" t="n">
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="123">
@@ -4108,7 +4111,7 @@
       <c r="F123" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="7" t="n">
+      <c r="G123" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4132,13 +4135,13 @@
         <v>22</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G124" s="14" t="n">
+        <v>0.5909090909090909</v>
       </c>
     </row>
     <row r="125">
@@ -4161,13 +4164,13 @@
         <v>30</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="7" t="n">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G125" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="126">
@@ -4190,13 +4193,13 @@
         <v>13</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G126" s="14" t="n">
+        <v>0.4615384615384615</v>
       </c>
     </row>
     <row r="127">
@@ -4219,13 +4222,13 @@
         <v>58</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="F127" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G127" s="11" t="n">
-        <v>0.896551724137931</v>
+        <v>41</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G127" s="13" t="n">
+        <v>0.7068965517241379</v>
       </c>
     </row>
     <row r="128">
@@ -4248,13 +4251,13 @@
         <v>34</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="4" t="n">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="129">
@@ -4282,7 +4285,7 @@
       <c r="F129" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G129" s="7" t="n">
+      <c r="G129" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4306,13 +4309,13 @@
         <v>32</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.78125</v>
       </c>
     </row>
     <row r="131">
@@ -4340,7 +4343,7 @@
       <c r="F131" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G131" s="7" t="n">
+      <c r="G131" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4364,13 +4367,13 @@
         <v>37</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="11" t="n">
+        <v>0.972972972972973</v>
       </c>
     </row>
     <row r="133">
@@ -4393,13 +4396,13 @@
         <v>37</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="7" t="n">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" s="15" t="n">
+        <v>0.8918918918918919</v>
       </c>
     </row>
     <row r="134">
@@ -4456,7 +4459,7 @@
       <c r="F135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G135" s="7" t="n">
+      <c r="G135" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4514,7 +4517,7 @@
       <c r="F137" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G137" s="7" t="n">
+      <c r="G137" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4567,13 +4570,13 @@
         <v>28</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="7" t="n">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="8" t="n">
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="140">
@@ -4596,13 +4599,13 @@
         <v>11</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="4" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G140" s="14" t="n">
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="141">
@@ -4625,13 +4628,13 @@
         <v>13</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F141" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="12" t="n">
-        <v>0.923076923076923</v>
+        <v>5</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G141" s="13" t="n">
+        <v>0.3846153846153847</v>
       </c>
     </row>
     <row r="142">
@@ -4654,13 +4657,13 @@
         <v>7</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F142" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G142" s="9" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G142" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -4683,13 +4686,13 @@
         <v>13</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F143" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="12" t="n">
-        <v>0.923076923076923</v>
+        <v>7</v>
+      </c>
+      <c r="F143" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G143" s="13" t="n">
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="144">
@@ -4712,34 +4715,34 @@
         <v>33</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F144" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G144" s="13" t="n">
-        <v>0.7878787878787878</v>
+        <v>17</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G144" s="14" t="n">
+        <v>0.5151515151515151</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="15" t="inlineStr"/>
-      <c r="B145" s="16" t="inlineStr">
+      <c r="A145" s="16" t="inlineStr"/>
+      <c r="B145" s="17" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="C145" s="15" t="inlineStr"/>
-      <c r="D145" s="17" t="n">
+      <c r="C145" s="16" t="inlineStr"/>
+      <c r="D145" s="18" t="n">
         <v>6538</v>
       </c>
-      <c r="E145" s="17" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F145" s="17" t="n">
-        <v>74</v>
-      </c>
-      <c r="G145" s="18" t="n">
-        <v>0.9886815539920465</v>
+      <c r="E145" s="18" t="n">
+        <v>5627</v>
+      </c>
+      <c r="F145" s="18" t="n">
+        <v>911</v>
+      </c>
+      <c r="G145" s="19" t="n">
+        <v>0.8606607525237076</v>
       </c>
     </row>
   </sheetData>
